--- a/input/mapping/029. OCB_GOLD_TCKH_V_SLNV_UPL_HOP.xlsx
+++ b/input/mapping/029. OCB_GOLD_TCKH_V_SLNV_UPL_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/HOP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="889" documentId="13_ncr:1_{B2FE61F2-C065-4E3F-B7A6-32E71A926C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF2F59D7-B423-4015-90C4-A5D943108261}"/>
+  <xr:revisionPtr revIDLastSave="894" documentId="13_ncr:1_{B2FE61F2-C065-4E3F-B7A6-32E71A926C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8596125-6185-4702-8B1A-FA347DB74E48}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -2582,6 +2582,132 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2621,132 +2747,6 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2771,14 +2771,12 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3152,489 +3150,489 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="30" customHeight="1">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="149" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
-      <c r="AC1" s="107"/>
-      <c r="AD1" s="107"/>
-      <c r="AE1" s="107"/>
-      <c r="AF1" s="107"/>
-      <c r="AG1" s="107"/>
-      <c r="AH1" s="107"/>
-      <c r="AI1" s="107"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
+      <c r="W1" s="149"/>
+      <c r="X1" s="149"/>
+      <c r="Y1" s="149"/>
+      <c r="Z1" s="149"/>
+      <c r="AA1" s="149"/>
+      <c r="AB1" s="149"/>
+      <c r="AC1" s="149"/>
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="149"/>
+      <c r="AG1" s="149"/>
+      <c r="AH1" s="149"/>
+      <c r="AI1" s="149"/>
     </row>
     <row r="2" spans="1:35" ht="8.1" customHeight="1"/>
     <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="105"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="106"/>
-      <c r="F3" s="104" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="148"/>
+      <c r="F3" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="106"/>
-      <c r="K3" s="108" t="s">
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="148"/>
+      <c r="K3" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="109"/>
-      <c r="M3" s="109"/>
-      <c r="N3" s="110"/>
-      <c r="P3" s="98" t="s">
+      <c r="L3" s="151"/>
+      <c r="M3" s="151"/>
+      <c r="N3" s="152"/>
+      <c r="P3" s="140" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="100"/>
-      <c r="U3" s="101" t="s">
+      <c r="Q3" s="141"/>
+      <c r="R3" s="141"/>
+      <c r="S3" s="142"/>
+      <c r="U3" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="V3" s="102"/>
-      <c r="W3" s="102"/>
-      <c r="X3" s="103"/>
-      <c r="Z3" s="101" t="s">
+      <c r="V3" s="144"/>
+      <c r="W3" s="144"/>
+      <c r="X3" s="145"/>
+      <c r="Z3" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="AA3" s="102"/>
-      <c r="AB3" s="102"/>
-      <c r="AC3" s="103"/>
+      <c r="AA3" s="144"/>
+      <c r="AB3" s="144"/>
+      <c r="AC3" s="145"/>
     </row>
     <row r="4" spans="1:35" ht="6" customHeight="1"/>
     <row r="5" spans="1:35" ht="18" customHeight="1">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="F5" s="135" t="s">
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="F5" s="127" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="135"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
       <c r="J5" s="31"/>
-      <c r="K5" s="137" t="s">
+      <c r="K5" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="137"/>
-      <c r="M5" s="137"/>
-      <c r="N5" s="137"/>
+      <c r="L5" s="129"/>
+      <c r="M5" s="129"/>
+      <c r="N5" s="129"/>
       <c r="O5" s="31"/>
-      <c r="P5" s="133" t="s">
+      <c r="P5" s="125" t="s">
         <v>10</v>
       </c>
-      <c r="Q5" s="133"/>
-      <c r="R5" s="133"/>
-      <c r="S5" s="133"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="125"/>
       <c r="T5" s="31"/>
-      <c r="U5" s="131" t="s">
+      <c r="U5" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="V5" s="131"/>
-      <c r="W5" s="131"/>
-      <c r="X5" s="131"/>
-      <c r="Z5" s="113" t="s">
+      <c r="V5" s="123"/>
+      <c r="W5" s="123"/>
+      <c r="X5" s="123"/>
+      <c r="Z5" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="AA5" s="114"/>
-      <c r="AB5" s="114"/>
-      <c r="AC5" s="115"/>
+      <c r="AA5" s="106"/>
+      <c r="AB5" s="106"/>
+      <c r="AC5" s="107"/>
     </row>
     <row r="6" spans="1:35" ht="18" customHeight="1">
-      <c r="A6" s="111"/>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
+      <c r="A6" s="103"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="F6" s="128"/>
+      <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
       <c r="J6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="138"/>
-      <c r="L6" s="138"/>
-      <c r="M6" s="138"/>
-      <c r="N6" s="138"/>
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
+      <c r="M6" s="130"/>
+      <c r="N6" s="130"/>
       <c r="O6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="P6" s="134"/>
-      <c r="Q6" s="134"/>
-      <c r="R6" s="134"/>
-      <c r="S6" s="134"/>
+      <c r="P6" s="126"/>
+      <c r="Q6" s="126"/>
+      <c r="R6" s="126"/>
+      <c r="S6" s="126"/>
       <c r="T6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="132"/>
-      <c r="V6" s="132"/>
-      <c r="W6" s="132"/>
-      <c r="X6" s="132"/>
+      <c r="U6" s="124"/>
+      <c r="V6" s="124"/>
+      <c r="W6" s="124"/>
+      <c r="X6" s="124"/>
       <c r="Y6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="Z6" s="116"/>
-      <c r="AA6" s="117"/>
-      <c r="AB6" s="117"/>
-      <c r="AC6" s="118"/>
+      <c r="Z6" s="108"/>
+      <c r="AA6" s="109"/>
+      <c r="AB6" s="109"/>
+      <c r="AC6" s="110"/>
     </row>
     <row r="7" spans="1:35" ht="18" customHeight="1">
-      <c r="A7" s="111"/>
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="F7" s="136"/>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
+      <c r="A7" s="103"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
       <c r="J7" s="31"/>
-      <c r="K7" s="138"/>
-      <c r="L7" s="138"/>
-      <c r="M7" s="138"/>
-      <c r="N7" s="138"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="130"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="130"/>
       <c r="O7" s="31"/>
-      <c r="P7" s="134"/>
-      <c r="Q7" s="134"/>
-      <c r="R7" s="134"/>
-      <c r="S7" s="134"/>
+      <c r="P7" s="126"/>
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126"/>
+      <c r="S7" s="126"/>
       <c r="T7" s="31"/>
-      <c r="U7" s="132"/>
-      <c r="V7" s="132"/>
-      <c r="W7" s="132"/>
-      <c r="X7" s="132"/>
-      <c r="Z7" s="119"/>
-      <c r="AA7" s="120"/>
-      <c r="AB7" s="120"/>
-      <c r="AC7" s="121"/>
+      <c r="U7" s="124"/>
+      <c r="V7" s="124"/>
+      <c r="W7" s="124"/>
+      <c r="X7" s="124"/>
+      <c r="Z7" s="111"/>
+      <c r="AA7" s="112"/>
+      <c r="AB7" s="112"/>
+      <c r="AC7" s="113"/>
     </row>
     <row r="8" spans="1:35" ht="18" customHeight="1">
-      <c r="A8" s="111"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="136"/>
-      <c r="I8" s="136"/>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="138"/>
-      <c r="N8" s="138"/>
-      <c r="P8" s="134"/>
-      <c r="Q8" s="134"/>
-      <c r="R8" s="134"/>
-      <c r="S8" s="134"/>
-      <c r="U8" s="132"/>
-      <c r="V8" s="132"/>
-      <c r="W8" s="132"/>
-      <c r="X8" s="132"/>
+      <c r="A8" s="103"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="130"/>
+      <c r="M8" s="130"/>
+      <c r="N8" s="130"/>
+      <c r="P8" s="126"/>
+      <c r="Q8" s="126"/>
+      <c r="R8" s="126"/>
+      <c r="S8" s="126"/>
+      <c r="U8" s="124"/>
+      <c r="V8" s="124"/>
+      <c r="W8" s="124"/>
+      <c r="X8" s="124"/>
     </row>
     <row r="9" spans="1:35" ht="18" customHeight="1">
-      <c r="A9" s="111"/>
-      <c r="B9" s="111"/>
-      <c r="C9" s="111"/>
-      <c r="D9" s="111"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="136"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="136"/>
+      <c r="A9" s="103"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
       <c r="J9" s="31"/>
-      <c r="K9" s="138"/>
-      <c r="L9" s="138"/>
-      <c r="M9" s="138"/>
-      <c r="N9" s="138"/>
-      <c r="P9" s="134"/>
-      <c r="Q9" s="134"/>
-      <c r="R9" s="134"/>
-      <c r="S9" s="134"/>
-      <c r="U9" s="132"/>
-      <c r="V9" s="132"/>
-      <c r="W9" s="132"/>
-      <c r="X9" s="132"/>
-      <c r="Z9" s="122" t="s">
+      <c r="K9" s="130"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="130"/>
+      <c r="P9" s="126"/>
+      <c r="Q9" s="126"/>
+      <c r="R9" s="126"/>
+      <c r="S9" s="126"/>
+      <c r="U9" s="124"/>
+      <c r="V9" s="124"/>
+      <c r="W9" s="124"/>
+      <c r="X9" s="124"/>
+      <c r="Z9" s="114" t="s">
         <v>14</v>
       </c>
-      <c r="AA9" s="123"/>
-      <c r="AB9" s="123"/>
-      <c r="AC9" s="124"/>
+      <c r="AA9" s="115"/>
+      <c r="AB9" s="115"/>
+      <c r="AC9" s="116"/>
     </row>
     <row r="10" spans="1:35" ht="18" customHeight="1">
-      <c r="A10" s="111"/>
-      <c r="B10" s="111"/>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="F10" s="136"/>
-      <c r="G10" s="136"/>
-      <c r="H10" s="136"/>
-      <c r="I10" s="136"/>
+      <c r="A10" s="103"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
       <c r="J10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="138"/>
-      <c r="L10" s="138"/>
-      <c r="M10" s="138"/>
-      <c r="N10" s="138"/>
-      <c r="P10" s="134"/>
-      <c r="Q10" s="134"/>
-      <c r="R10" s="134"/>
-      <c r="S10" s="134"/>
-      <c r="U10" s="132"/>
-      <c r="V10" s="132"/>
-      <c r="W10" s="132"/>
-      <c r="X10" s="132"/>
+      <c r="K10" s="130"/>
+      <c r="L10" s="130"/>
+      <c r="M10" s="130"/>
+      <c r="N10" s="130"/>
+      <c r="P10" s="126"/>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="126"/>
+      <c r="S10" s="126"/>
+      <c r="U10" s="124"/>
+      <c r="V10" s="124"/>
+      <c r="W10" s="124"/>
+      <c r="X10" s="124"/>
       <c r="Y10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="Z10" s="125"/>
-      <c r="AA10" s="126"/>
-      <c r="AB10" s="126"/>
-      <c r="AC10" s="127"/>
+      <c r="Z10" s="117"/>
+      <c r="AA10" s="118"/>
+      <c r="AB10" s="118"/>
+      <c r="AC10" s="119"/>
     </row>
     <row r="11" spans="1:35" ht="18" customHeight="1">
-      <c r="A11" s="111"/>
-      <c r="B11" s="111"/>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="136"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="136"/>
+      <c r="A11" s="103"/>
+      <c r="B11" s="103"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
       <c r="J11" s="31"/>
-      <c r="K11" s="138"/>
-      <c r="L11" s="138"/>
-      <c r="M11" s="138"/>
-      <c r="N11" s="138"/>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
-      <c r="R11" s="134"/>
-      <c r="S11" s="134"/>
-      <c r="U11" s="132"/>
-      <c r="V11" s="132"/>
-      <c r="W11" s="132"/>
-      <c r="X11" s="132"/>
-      <c r="Z11" s="128"/>
-      <c r="AA11" s="129"/>
-      <c r="AB11" s="129"/>
-      <c r="AC11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
+      <c r="M11" s="130"/>
+      <c r="N11" s="130"/>
+      <c r="P11" s="126"/>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="126"/>
+      <c r="S11" s="126"/>
+      <c r="U11" s="124"/>
+      <c r="V11" s="124"/>
+      <c r="W11" s="124"/>
+      <c r="X11" s="124"/>
+      <c r="Z11" s="120"/>
+      <c r="AA11" s="121"/>
+      <c r="AB11" s="121"/>
+      <c r="AC11" s="122"/>
     </row>
     <row r="12" spans="1:35" ht="18" customHeight="1">
-      <c r="A12" s="111"/>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
+      <c r="A12" s="103"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
       <c r="E12" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="136"/>
-      <c r="G12" s="136"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="136"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="128"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="128"/>
     </row>
     <row r="13" spans="1:35" ht="18" customHeight="1">
-      <c r="A13" s="111"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="F13" s="136"/>
-      <c r="G13" s="136"/>
-      <c r="H13" s="136"/>
-      <c r="I13" s="136"/>
+      <c r="A13" s="103"/>
+      <c r="B13" s="103"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="128"/>
       <c r="J13" s="31"/>
-      <c r="K13" s="139" t="s">
+      <c r="K13" s="131" t="s">
         <v>15</v>
       </c>
-      <c r="L13" s="140"/>
-      <c r="M13" s="140"/>
-      <c r="N13" s="141"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="132"/>
+      <c r="N13" s="133"/>
     </row>
     <row r="14" spans="1:35" ht="18" customHeight="1">
-      <c r="A14" s="111"/>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="F14" s="136"/>
-      <c r="G14" s="136"/>
-      <c r="H14" s="136"/>
-      <c r="I14" s="136"/>
+      <c r="A14" s="103"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="128"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="128"/>
       <c r="J14" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="K14" s="142"/>
-      <c r="L14" s="143"/>
-      <c r="M14" s="143"/>
-      <c r="N14" s="144"/>
+      <c r="K14" s="134"/>
+      <c r="L14" s="135"/>
+      <c r="M14" s="135"/>
+      <c r="N14" s="136"/>
     </row>
     <row r="15" spans="1:35" ht="18" customHeight="1">
-      <c r="A15" s="111"/>
-      <c r="B15" s="111"/>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="136"/>
-      <c r="I15" s="136"/>
+      <c r="A15" s="103"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="F15" s="128"/>
+      <c r="G15" s="128"/>
+      <c r="H15" s="128"/>
+      <c r="I15" s="128"/>
       <c r="J15" s="31"/>
-      <c r="K15" s="145"/>
-      <c r="L15" s="146"/>
-      <c r="M15" s="146"/>
-      <c r="N15" s="147"/>
+      <c r="K15" s="137"/>
+      <c r="L15" s="138"/>
+      <c r="M15" s="138"/>
+      <c r="N15" s="139"/>
     </row>
     <row r="16" spans="1:35" ht="18" customHeight="1">
-      <c r="A16" s="111"/>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="F16" s="136"/>
-      <c r="G16" s="136"/>
-      <c r="H16" s="136"/>
-      <c r="I16" s="136"/>
+      <c r="A16" s="103"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="128"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
-      <c r="A17" s="111"/>
-      <c r="B17" s="111"/>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
+      <c r="A17" s="103"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="128"/>
       <c r="J17" s="31"/>
-      <c r="K17" s="139" t="s">
+      <c r="K17" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="140"/>
-      <c r="M17" s="140"/>
-      <c r="N17" s="141"/>
+      <c r="L17" s="132"/>
+      <c r="M17" s="132"/>
+      <c r="N17" s="133"/>
     </row>
     <row r="18" spans="1:15" ht="18" customHeight="1">
-      <c r="A18" s="111"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="111"/>
-      <c r="F18" s="136"/>
-      <c r="G18" s="136"/>
-      <c r="H18" s="136"/>
-      <c r="I18" s="136"/>
+      <c r="A18" s="103"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="128"/>
+      <c r="H18" s="128"/>
+      <c r="I18" s="128"/>
       <c r="J18" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="K18" s="142"/>
-      <c r="L18" s="143"/>
-      <c r="M18" s="143"/>
-      <c r="N18" s="144"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="135"/>
+      <c r="N18" s="136"/>
     </row>
     <row r="19" spans="1:15" ht="18" customHeight="1">
-      <c r="A19" s="111"/>
-      <c r="B19" s="111"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="136"/>
-      <c r="H19" s="136"/>
-      <c r="I19" s="136"/>
+      <c r="A19" s="103"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="103"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="128"/>
+      <c r="H19" s="128"/>
+      <c r="I19" s="128"/>
       <c r="J19" s="31"/>
-      <c r="K19" s="145"/>
-      <c r="L19" s="146"/>
-      <c r="M19" s="146"/>
-      <c r="N19" s="147"/>
+      <c r="K19" s="137"/>
+      <c r="L19" s="138"/>
+      <c r="M19" s="138"/>
+      <c r="N19" s="139"/>
     </row>
     <row r="20" spans="1:15" ht="18" customHeight="1">
-      <c r="A20" s="111"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="F20" s="136"/>
-      <c r="G20" s="136"/>
-      <c r="H20" s="136"/>
-      <c r="I20" s="136"/>
+      <c r="A20" s="103"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="128"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="128"/>
     </row>
     <row r="21" spans="1:15" ht="18" customHeight="1">
-      <c r="A21" s="111"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="F21" s="136"/>
-      <c r="G21" s="136"/>
-      <c r="H21" s="136"/>
-      <c r="I21" s="136"/>
+      <c r="A21" s="103"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="103"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="128"/>
+      <c r="I21" s="128"/>
       <c r="J21" s="31"/>
-      <c r="K21" s="139" t="s">
+      <c r="K21" s="131" t="s">
         <v>17</v>
       </c>
-      <c r="L21" s="140"/>
-      <c r="M21" s="140"/>
-      <c r="N21" s="141"/>
+      <c r="L21" s="132"/>
+      <c r="M21" s="132"/>
+      <c r="N21" s="133"/>
     </row>
     <row r="22" spans="1:15" ht="18" customHeight="1">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="F22" s="136"/>
-      <c r="G22" s="136"/>
-      <c r="H22" s="136"/>
-      <c r="I22" s="136"/>
+      <c r="A22" s="103"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="103"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="128"/>
+      <c r="H22" s="128"/>
+      <c r="I22" s="128"/>
       <c r="J22" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="142"/>
-      <c r="L22" s="143"/>
-      <c r="M22" s="143"/>
-      <c r="N22" s="144"/>
+      <c r="K22" s="134"/>
+      <c r="L22" s="135"/>
+      <c r="M22" s="135"/>
+      <c r="N22" s="136"/>
     </row>
     <row r="23" spans="1:15" ht="8.1" customHeight="1">
-      <c r="A23" s="111"/>
-      <c r="B23" s="111"/>
-      <c r="C23" s="111"/>
-      <c r="D23" s="111"/>
-      <c r="F23" s="136"/>
-      <c r="G23" s="136"/>
-      <c r="H23" s="136"/>
-      <c r="I23" s="136"/>
+      <c r="A23" s="103"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="103"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="128"/>
       <c r="J23" s="31"/>
-      <c r="K23" s="145"/>
-      <c r="L23" s="146"/>
-      <c r="M23" s="146"/>
-      <c r="N23" s="147"/>
+      <c r="K23" s="137"/>
+      <c r="L23" s="138"/>
+      <c r="M23" s="138"/>
+      <c r="N23" s="139"/>
     </row>
     <row r="24" spans="1:15" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="112"/>
+      <c r="B24" s="104"/>
       <c r="C24" s="162"/>
       <c r="D24" s="162"/>
-      <c r="E24" s="112"/>
+      <c r="E24" s="104"/>
       <c r="F24" s="162"/>
-      <c r="G24" s="112"/>
+      <c r="G24" s="104"/>
       <c r="H24" s="162"/>
       <c r="I24" s="162"/>
       <c r="J24" s="162"/>
@@ -3645,12 +3643,12 @@
       <c r="O24" s="162"/>
     </row>
     <row r="25" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B25" s="148"/>
+      <c r="B25" s="98"/>
       <c r="C25" s="162"/>
       <c r="D25" s="162"/>
-      <c r="E25" s="150"/>
+      <c r="E25" s="100"/>
       <c r="F25" s="162"/>
-      <c r="G25" s="149"/>
+      <c r="G25" s="99"/>
       <c r="H25" s="162"/>
       <c r="I25" s="162"/>
       <c r="J25" s="162"/>
@@ -3661,15 +3659,15 @@
       <c r="O25" s="162"/>
     </row>
     <row r="26" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B26" s="148"/>
+      <c r="B26" s="98"/>
       <c r="C26" s="162"/>
       <c r="D26" s="162"/>
-      <c r="E26" s="151" t="s">
+      <c r="E26" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
-      <c r="H26" s="152"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
       <c r="J26" s="50" t="s">
         <v>19</v>
       </c>
@@ -3678,7 +3676,7 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B27" s="148"/>
+      <c r="B27" s="98"/>
       <c r="C27" s="162"/>
       <c r="D27" s="162"/>
       <c r="E27" s="38"/>
@@ -3694,7 +3692,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B28" s="148"/>
+      <c r="B28" s="98"/>
       <c r="C28" s="162"/>
       <c r="D28" s="162"/>
       <c r="E28" s="40"/>
@@ -3710,7 +3708,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B29" s="148"/>
+      <c r="B29" s="98"/>
       <c r="C29" s="162"/>
       <c r="D29" s="162"/>
       <c r="E29" s="41"/>
@@ -3747,14 +3745,13 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G25:O25"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="F3:I3"/>
     <mergeCell ref="A5:D23"/>
     <mergeCell ref="G24:O24"/>
     <mergeCell ref="B24:D24"/>
@@ -3768,13 +3765,14 @@
     <mergeCell ref="K13:N15"/>
     <mergeCell ref="K17:N19"/>
     <mergeCell ref="K21:N23"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A1:AI1"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G25:O25"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:H26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3877,7 +3875,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="305.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -5327,13 +5325,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5509,16 +5506,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63EC841B-EE2F-404B-AE20-759328EC6A01}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F5D78C1-8A47-4B3E-B0AF-72715DE99B9C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5526,5 +5524,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F5D78C1-8A47-4B3E-B0AF-72715DE99B9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63EC841B-EE2F-404B-AE20-759328EC6A01}"/>
 </file>
--- a/input/mapping/029. OCB_GOLD_TCKH_V_SLNV_UPL_HOP.xlsx
+++ b/input/mapping/029. OCB_GOLD_TCKH_V_SLNV_UPL_HOP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/HOP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="894" documentId="13_ncr:1_{B2FE61F2-C065-4E3F-B7A6-32E71A926C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8596125-6185-4702-8B1A-FA347DB74E48}"/>
+  <xr:revisionPtr revIDLastSave="902" documentId="13_ncr:1_{B2FE61F2-C065-4E3F-B7A6-32E71A926C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DEBC740-A44B-4513-81F3-F70C4317DCC4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -466,8 +466,7 @@
     , 'DIEU CHINH' AS BRANCH_NAME
     , 'VN1000000'  AS BRANCH_CODE
     , 'VN1000000'  AS PRN_BRANCH_CODE
-    , NULL         AS OU_ID
-;</t>
+    , NULL         AS OU_ID</t>
   </si>
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
@@ -477,37 +476,17 @@
       dim.OU_ID           AS OU_ID
     , dim.OU_CODE         AS BRANCH_CODE
     , dim.OU_NM           AS BRANCH_NAME
-    , dim.PRN_OU_CODE     AS PRN_BRANCH_CODE
-    , dim.PRN_OU_NM       AS PRN_BRANCH_NAME
+    , nvl(dim.PRN_OU_CODE, dim.OU_CODE)     AS PRN_BRANCH_CODE
+    , nvl(dim.PRN_OU_NM, dim.OU_NM)       AS PRN_BRANCH_NAME
 FROM CB_OU_DIM dim
-WHERE dim.EFF_TO_DT IS NULL   -- SCD2: chỉ lấy bản ghi còn hiệu lực (NULL = chưa đóng)
-;</t>
+WHERE dim.EFF_TO_DT IS NULL   -- SCD2: chỉ lấy bản ghi còn hiệu lực (NULL = chưa đóng)</t>
   </si>
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CB_OU_DIM (
-    OU_DIM_ID       BIGINT,     -- MAX(OU_DIM_ID) + ROW_NUMBER()
-    OU_ID           STRING,     -- branch_hashkey (SHA256)
-    OU_NM           STRING,
-    OU_CODE         STRING,
-    PRN_OU_ID       STRING,
-    PRN_OU_NM       STRING,
-    PRN_OU_CODE     STRING,
-    CB_AREA_ID      INTEGER,
-    CB_AREA_NM      STRING,
-    CRT_TM          TIMESTAMP,
-    EFF_FM_DT       DATE,
-    EFF_TO_DT       DATE,
-    START_WK_DT     DATE,
-    OU_ADR          STRING,
-    OU_PH           STRING
-)
-USING DELTA;
 MERGE INTO CB_OU_DIM tgt
 USING (
     WITH
-    -- STS Hub: khóa có trạng thái mới nhất = 'D' (đã xóa) đến :etl_date
     sts_deleted AS (
         SELECT branch_hashkey
         FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
@@ -515,15 +494,12 @@
         GROUP BY branch_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Hub đang có hiệu lực = Hub LEFT JOIN loại các khóa deleted
     hub_active AS (
         SELECT h.branch_hashkey, h.business_key, h.source_event_date
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch') h
-        LEFT JOIN sts_deleted d
-            ON h.branch_hashkey = d.branch_hashkey
+        LEFT JOIN sts_deleted d ON h.branch_hashkey = d.branch_hashkey
         WHERE d.branch_hashkey IS NULL
     ),
-    -- Satellite (single-active): làm giàu thuộc tính, bản mới nhất đến :etl_date
     sat_latest AS (
         SELECT
             branch_hashkey,
@@ -532,7 +508,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- Satellite branch_mapping (single-active)
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -543,18 +518,23 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
+    area_map AS (
+        SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+        FROM ou_area_mapping
+        WHERE CB_AREA_ID IS NOT NULL
+    ),
     source_data AS (
         SELECT
-            h.branch_hashkey                                    AS OU_ID,
-            h.business_key                                      AS OU_CODE,
-            SUBSTRING_INDEX(si.t_company_name, '::', 1)         AS OU_NM,
-            prn_hub.branch_hashkey                              AS PRN_OU_ID,
-            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)     AS PRN_OU_NM,
-            bm.parent_branch_code                               AS PRN_OU_CODE,
+            h.branch_hashkey                                AS OU_ID,
+            h.business_key                                  AS OU_CODE,
+            SUBSTRING_INDEX(si.t_company_name, '::', 1)     AS OU_NM,
+            prn_hub.branch_hashkey                          AS PRN_OU_ID,
+            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1) AS PRN_OU_NM,
+            bm.parent_branch_code                           AS PRN_OU_CODE,
             am.CB_AREA_ID,
             am.CB_AREA_NM,
-            bm.address                                          AS OU_ADR,
-            bm.phone_number                                     AS OU_PH,
+            bm.address                                      AS OU_ADR,
+            bm.phone_number                                 AS OU_PH,
             h.source_event_date
         FROM hub_active h
         LEFT JOIN sat_latest si
@@ -565,15 +545,10 @@
             ON prn_hub.business_key = bm.parent_branch_code
         LEFT JOIN sat_latest prn_si
             ON prn_hub.branch_hashkey = prn_si.branch_hashkey
-        LEFT JOIN ou_area_mapping am
+        LEFT JOIN area_map am
             ON am.OU_ID = h.business_key
         WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
           AND h.business_key &lt;&gt; 'VN0010001'
-    ),
-    -- Max OU_DIM_ID hiện tại
-    max_id AS (
-        SELECT COALESCE(MAX(OU_DIM_ID), 0) AS max_val
-        FROM CB_OU_DIM
     ),
     changed AS (
         SELECT src.OU_ID
@@ -603,9 +578,8 @@
             src.source_event_date,
             src.OU_ADR,
             src.OU_PH,
-            m.max_val + ROW_NUMBER() OVER (ORDER BY src.OU_ID)  AS NEW_OU_DIM_ID
+            uuid()                                              AS NEW_OU_DIM_ID
         FROM source_data src
-        CROSS JOIN max_id m
         LEFT JOIN CB_OU_DIM tgt_chk
             ON  src.OU_ID        = tgt_chk.OU_ID
             AND tgt_chk.EFF_TO_DT IS NULL
@@ -614,8 +588,8 @@
     ),
     close_records AS (
         SELECT
-            'CLOSE'                                             AS rec_type,
-            'D'                                                 AS CDC_FLAG,
+            'CLOSE'                AS rec_type,
+            'D'                    AS CDC_FLAG,
             tgt.OU_ID,
             tgt.OU_NM,
             tgt.OU_CODE,
@@ -624,10 +598,10 @@
             tgt.PRN_OU_CODE,
             tgt.CB_AREA_ID,
             tgt.CB_AREA_NM,
-            tgt.START_WK_DT                                     AS source_event_date,
+            tgt.START_WK_DT        AS source_event_date,
             tgt.OU_ADR,
             tgt.OU_PH,
-            tgt.OU_DIM_ID                                       AS NEW_OU_DIM_ID
+            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID 
         FROM CB_OU_DIM tgt
         LEFT JOIN source_data src ON src.OU_ID = tgt.OU_ID
         WHERE tgt.EFF_TO_DT IS NULL
@@ -636,9 +610,25 @@
                 OR src.OU_ID IS NULL
               )
     )
-    SELECT * FROM new_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM new_records
     UNION ALL
-    SELECT * FROM close_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM close_records
 ) src
 ON  tgt.OU_ID     = src.OU_ID
 AND tgt.EFF_TO_DT IS NULL
@@ -672,8 +662,7 @@
 WHEN MATCHED AND src.rec_type = 'CLOSE' THEN
     UPDATE SET
         tgt.EFF_TO_DT = DATE_SUB(TO_DATE(:etl_date, 'yyyyMMdd'), 1),
-        tgt.CRT_TM    = CURRENT_TIMESTAMP()
-;</t>
+        tgt.CRT_TM    = CURRENT_TIMESTAMP()</t>
   </si>
   <si>
     <t>JOIN SCHEMA</t>
@@ -2315,7 +2304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2582,6 +2571,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2597,156 +2736,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2772,6 +2761,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
@@ -3150,524 +3140,524 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="30" customHeight="1">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
-      <c r="K1" s="149"/>
-      <c r="L1" s="149"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="149"/>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="149"/>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="149"/>
-      <c r="W1" s="149"/>
-      <c r="X1" s="149"/>
-      <c r="Y1" s="149"/>
-      <c r="Z1" s="149"/>
-      <c r="AA1" s="149"/>
-      <c r="AB1" s="149"/>
-      <c r="AC1" s="149"/>
-      <c r="AD1" s="149"/>
-      <c r="AE1" s="149"/>
-      <c r="AF1" s="149"/>
-      <c r="AG1" s="149"/>
-      <c r="AH1" s="149"/>
-      <c r="AI1" s="149"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
+      <c r="AC1" s="107"/>
+      <c r="AD1" s="107"/>
+      <c r="AE1" s="107"/>
+      <c r="AF1" s="107"/>
+      <c r="AG1" s="107"/>
+      <c r="AH1" s="107"/>
+      <c r="AI1" s="107"/>
     </row>
     <row r="2" spans="1:35" ht="8.1" customHeight="1"/>
     <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="146" t="s">
+      <c r="A3" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="148"/>
-      <c r="F3" s="146" t="s">
+      <c r="B3" s="105"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="106"/>
+      <c r="F3" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="147"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="148"/>
-      <c r="K3" s="150" t="s">
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="106"/>
+      <c r="K3" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="151"/>
-      <c r="M3" s="151"/>
-      <c r="N3" s="152"/>
-      <c r="P3" s="140" t="s">
+      <c r="L3" s="109"/>
+      <c r="M3" s="109"/>
+      <c r="N3" s="110"/>
+      <c r="P3" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="141"/>
-      <c r="R3" s="141"/>
-      <c r="S3" s="142"/>
-      <c r="U3" s="143" t="s">
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="100"/>
+      <c r="U3" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="V3" s="144"/>
-      <c r="W3" s="144"/>
-      <c r="X3" s="145"/>
-      <c r="Z3" s="143" t="s">
+      <c r="V3" s="102"/>
+      <c r="W3" s="102"/>
+      <c r="X3" s="103"/>
+      <c r="Z3" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="AA3" s="144"/>
-      <c r="AB3" s="144"/>
-      <c r="AC3" s="145"/>
+      <c r="AA3" s="102"/>
+      <c r="AB3" s="102"/>
+      <c r="AC3" s="103"/>
     </row>
     <row r="4" spans="1:35" ht="6" customHeight="1"/>
     <row r="5" spans="1:35" ht="18" customHeight="1">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="F5" s="127" t="s">
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="F5" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="127"/>
+      <c r="G5" s="135"/>
+      <c r="H5" s="135"/>
+      <c r="I5" s="135"/>
       <c r="J5" s="31"/>
-      <c r="K5" s="129" t="s">
+      <c r="K5" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="129"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="129"/>
+      <c r="L5" s="137"/>
+      <c r="M5" s="137"/>
+      <c r="N5" s="137"/>
       <c r="O5" s="31"/>
-      <c r="P5" s="125" t="s">
+      <c r="P5" s="133" t="s">
         <v>10</v>
       </c>
-      <c r="Q5" s="125"/>
-      <c r="R5" s="125"/>
-      <c r="S5" s="125"/>
+      <c r="Q5" s="133"/>
+      <c r="R5" s="133"/>
+      <c r="S5" s="133"/>
       <c r="T5" s="31"/>
-      <c r="U5" s="123" t="s">
+      <c r="U5" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="V5" s="123"/>
-      <c r="W5" s="123"/>
-      <c r="X5" s="123"/>
-      <c r="Z5" s="105" t="s">
+      <c r="V5" s="131"/>
+      <c r="W5" s="131"/>
+      <c r="X5" s="131"/>
+      <c r="Z5" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="AA5" s="106"/>
-      <c r="AB5" s="106"/>
-      <c r="AC5" s="107"/>
+      <c r="AA5" s="114"/>
+      <c r="AB5" s="114"/>
+      <c r="AC5" s="115"/>
     </row>
     <row r="6" spans="1:35" ht="18" customHeight="1">
-      <c r="A6" s="103"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="F6" s="128"/>
-      <c r="G6" s="128"/>
-      <c r="H6" s="128"/>
-      <c r="I6" s="128"/>
+      <c r="A6" s="111"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
       <c r="J6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
+      <c r="K6" s="138"/>
+      <c r="L6" s="138"/>
+      <c r="M6" s="138"/>
+      <c r="N6" s="138"/>
       <c r="O6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="P6" s="126"/>
-      <c r="Q6" s="126"/>
-      <c r="R6" s="126"/>
-      <c r="S6" s="126"/>
+      <c r="P6" s="134"/>
+      <c r="Q6" s="134"/>
+      <c r="R6" s="134"/>
+      <c r="S6" s="134"/>
       <c r="T6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="124"/>
-      <c r="V6" s="124"/>
-      <c r="W6" s="124"/>
-      <c r="X6" s="124"/>
+      <c r="U6" s="132"/>
+      <c r="V6" s="132"/>
+      <c r="W6" s="132"/>
+      <c r="X6" s="132"/>
       <c r="Y6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="Z6" s="108"/>
-      <c r="AA6" s="109"/>
-      <c r="AB6" s="109"/>
-      <c r="AC6" s="110"/>
+      <c r="Z6" s="116"/>
+      <c r="AA6" s="117"/>
+      <c r="AB6" s="117"/>
+      <c r="AC6" s="118"/>
     </row>
     <row r="7" spans="1:35" ht="18" customHeight="1">
-      <c r="A7" s="103"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
+      <c r="A7" s="111"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
       <c r="J7" s="31"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="138"/>
+      <c r="M7" s="138"/>
+      <c r="N7" s="138"/>
       <c r="O7" s="31"/>
-      <c r="P7" s="126"/>
-      <c r="Q7" s="126"/>
-      <c r="R7" s="126"/>
-      <c r="S7" s="126"/>
+      <c r="P7" s="134"/>
+      <c r="Q7" s="134"/>
+      <c r="R7" s="134"/>
+      <c r="S7" s="134"/>
       <c r="T7" s="31"/>
-      <c r="U7" s="124"/>
-      <c r="V7" s="124"/>
-      <c r="W7" s="124"/>
-      <c r="X7" s="124"/>
-      <c r="Z7" s="111"/>
-      <c r="AA7" s="112"/>
-      <c r="AB7" s="112"/>
-      <c r="AC7" s="113"/>
+      <c r="U7" s="132"/>
+      <c r="V7" s="132"/>
+      <c r="W7" s="132"/>
+      <c r="X7" s="132"/>
+      <c r="Z7" s="119"/>
+      <c r="AA7" s="120"/>
+      <c r="AB7" s="120"/>
+      <c r="AC7" s="121"/>
     </row>
     <row r="8" spans="1:35" ht="18" customHeight="1">
-      <c r="A8" s="103"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="F8" s="128"/>
-      <c r="G8" s="128"/>
-      <c r="H8" s="128"/>
-      <c r="I8" s="128"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="130"/>
-      <c r="N8" s="130"/>
-      <c r="P8" s="126"/>
-      <c r="Q8" s="126"/>
-      <c r="R8" s="126"/>
-      <c r="S8" s="126"/>
-      <c r="U8" s="124"/>
-      <c r="V8" s="124"/>
-      <c r="W8" s="124"/>
-      <c r="X8" s="124"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="F8" s="136"/>
+      <c r="G8" s="136"/>
+      <c r="H8" s="136"/>
+      <c r="I8" s="136"/>
+      <c r="K8" s="138"/>
+      <c r="L8" s="138"/>
+      <c r="M8" s="138"/>
+      <c r="N8" s="138"/>
+      <c r="P8" s="134"/>
+      <c r="Q8" s="134"/>
+      <c r="R8" s="134"/>
+      <c r="S8" s="134"/>
+      <c r="U8" s="132"/>
+      <c r="V8" s="132"/>
+      <c r="W8" s="132"/>
+      <c r="X8" s="132"/>
     </row>
     <row r="9" spans="1:35" ht="18" customHeight="1">
-      <c r="A9" s="103"/>
-      <c r="B9" s="103"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="128"/>
+      <c r="A9" s="111"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="F9" s="136"/>
+      <c r="G9" s="136"/>
+      <c r="H9" s="136"/>
+      <c r="I9" s="136"/>
       <c r="J9" s="31"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="130"/>
-      <c r="N9" s="130"/>
-      <c r="P9" s="126"/>
-      <c r="Q9" s="126"/>
-      <c r="R9" s="126"/>
-      <c r="S9" s="126"/>
-      <c r="U9" s="124"/>
-      <c r="V9" s="124"/>
-      <c r="W9" s="124"/>
-      <c r="X9" s="124"/>
-      <c r="Z9" s="114" t="s">
+      <c r="K9" s="138"/>
+      <c r="L9" s="138"/>
+      <c r="M9" s="138"/>
+      <c r="N9" s="138"/>
+      <c r="P9" s="134"/>
+      <c r="Q9" s="134"/>
+      <c r="R9" s="134"/>
+      <c r="S9" s="134"/>
+      <c r="U9" s="132"/>
+      <c r="V9" s="132"/>
+      <c r="W9" s="132"/>
+      <c r="X9" s="132"/>
+      <c r="Z9" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="AA9" s="115"/>
-      <c r="AB9" s="115"/>
-      <c r="AC9" s="116"/>
+      <c r="AA9" s="123"/>
+      <c r="AB9" s="123"/>
+      <c r="AC9" s="124"/>
     </row>
     <row r="10" spans="1:35" ht="18" customHeight="1">
-      <c r="A10" s="103"/>
-      <c r="B10" s="103"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="F10" s="128"/>
-      <c r="G10" s="128"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
+      <c r="A10" s="111"/>
+      <c r="B10" s="111"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="F10" s="136"/>
+      <c r="G10" s="136"/>
+      <c r="H10" s="136"/>
+      <c r="I10" s="136"/>
       <c r="J10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="130"/>
-      <c r="L10" s="130"/>
-      <c r="M10" s="130"/>
-      <c r="N10" s="130"/>
-      <c r="P10" s="126"/>
-      <c r="Q10" s="126"/>
-      <c r="R10" s="126"/>
-      <c r="S10" s="126"/>
-      <c r="U10" s="124"/>
-      <c r="V10" s="124"/>
-      <c r="W10" s="124"/>
-      <c r="X10" s="124"/>
+      <c r="K10" s="138"/>
+      <c r="L10" s="138"/>
+      <c r="M10" s="138"/>
+      <c r="N10" s="138"/>
+      <c r="P10" s="134"/>
+      <c r="Q10" s="134"/>
+      <c r="R10" s="134"/>
+      <c r="S10" s="134"/>
+      <c r="U10" s="132"/>
+      <c r="V10" s="132"/>
+      <c r="W10" s="132"/>
+      <c r="X10" s="132"/>
       <c r="Y10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="Z10" s="117"/>
-      <c r="AA10" s="118"/>
-      <c r="AB10" s="118"/>
-      <c r="AC10" s="119"/>
+      <c r="Z10" s="125"/>
+      <c r="AA10" s="126"/>
+      <c r="AB10" s="126"/>
+      <c r="AC10" s="127"/>
     </row>
     <row r="11" spans="1:35" ht="18" customHeight="1">
-      <c r="A11" s="103"/>
-      <c r="B11" s="103"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="128"/>
+      <c r="A11" s="111"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="136"/>
+      <c r="H11" s="136"/>
+      <c r="I11" s="136"/>
       <c r="J11" s="31"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="130"/>
-      <c r="N11" s="130"/>
-      <c r="P11" s="126"/>
-      <c r="Q11" s="126"/>
-      <c r="R11" s="126"/>
-      <c r="S11" s="126"/>
-      <c r="U11" s="124"/>
-      <c r="V11" s="124"/>
-      <c r="W11" s="124"/>
-      <c r="X11" s="124"/>
-      <c r="Z11" s="120"/>
-      <c r="AA11" s="121"/>
-      <c r="AB11" s="121"/>
-      <c r="AC11" s="122"/>
+      <c r="K11" s="138"/>
+      <c r="L11" s="138"/>
+      <c r="M11" s="138"/>
+      <c r="N11" s="138"/>
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
+      <c r="R11" s="134"/>
+      <c r="S11" s="134"/>
+      <c r="U11" s="132"/>
+      <c r="V11" s="132"/>
+      <c r="W11" s="132"/>
+      <c r="X11" s="132"/>
+      <c r="Z11" s="128"/>
+      <c r="AA11" s="129"/>
+      <c r="AB11" s="129"/>
+      <c r="AC11" s="130"/>
     </row>
     <row r="12" spans="1:35" ht="18" customHeight="1">
-      <c r="A12" s="103"/>
-      <c r="B12" s="103"/>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
+      <c r="A12" s="111"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
       <c r="E12" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="128"/>
-      <c r="G12" s="128"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="128"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
     </row>
     <row r="13" spans="1:35" ht="18" customHeight="1">
-      <c r="A13" s="103"/>
-      <c r="B13" s="103"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
-      <c r="F13" s="128"/>
-      <c r="G13" s="128"/>
-      <c r="H13" s="128"/>
-      <c r="I13" s="128"/>
+      <c r="A13" s="111"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="F13" s="136"/>
+      <c r="G13" s="136"/>
+      <c r="H13" s="136"/>
+      <c r="I13" s="136"/>
       <c r="J13" s="31"/>
-      <c r="K13" s="131" t="s">
+      <c r="K13" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="L13" s="132"/>
-      <c r="M13" s="132"/>
-      <c r="N13" s="133"/>
+      <c r="L13" s="140"/>
+      <c r="M13" s="140"/>
+      <c r="N13" s="141"/>
     </row>
     <row r="14" spans="1:35" ht="18" customHeight="1">
-      <c r="A14" s="103"/>
-      <c r="B14" s="103"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
-      <c r="I14" s="128"/>
+      <c r="A14" s="111"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="136"/>
+      <c r="H14" s="136"/>
+      <c r="I14" s="136"/>
       <c r="J14" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="K14" s="134"/>
-      <c r="L14" s="135"/>
-      <c r="M14" s="135"/>
-      <c r="N14" s="136"/>
+      <c r="K14" s="142"/>
+      <c r="L14" s="143"/>
+      <c r="M14" s="143"/>
+      <c r="N14" s="144"/>
     </row>
     <row r="15" spans="1:35" ht="18" customHeight="1">
-      <c r="A15" s="103"/>
-      <c r="B15" s="103"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128"/>
-      <c r="I15" s="128"/>
+      <c r="A15" s="111"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="136"/>
+      <c r="H15" s="136"/>
+      <c r="I15" s="136"/>
       <c r="J15" s="31"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="138"/>
-      <c r="M15" s="138"/>
-      <c r="N15" s="139"/>
+      <c r="K15" s="145"/>
+      <c r="L15" s="146"/>
+      <c r="M15" s="146"/>
+      <c r="N15" s="147"/>
     </row>
     <row r="16" spans="1:35" ht="18" customHeight="1">
-      <c r="A16" s="103"/>
-      <c r="B16" s="103"/>
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="F16" s="128"/>
-      <c r="G16" s="128"/>
-      <c r="H16" s="128"/>
-      <c r="I16" s="128"/>
+      <c r="A16" s="111"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="F16" s="136"/>
+      <c r="G16" s="136"/>
+      <c r="H16" s="136"/>
+      <c r="I16" s="136"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
-      <c r="A17" s="103"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="F17" s="128"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="128"/>
-      <c r="I17" s="128"/>
+      <c r="A17" s="111"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
       <c r="J17" s="31"/>
-      <c r="K17" s="131" t="s">
+      <c r="K17" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="132"/>
-      <c r="M17" s="132"/>
-      <c r="N17" s="133"/>
+      <c r="L17" s="140"/>
+      <c r="M17" s="140"/>
+      <c r="N17" s="141"/>
     </row>
     <row r="18" spans="1:15" ht="18" customHeight="1">
-      <c r="A18" s="103"/>
-      <c r="B18" s="103"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="103"/>
-      <c r="F18" s="128"/>
-      <c r="G18" s="128"/>
-      <c r="H18" s="128"/>
-      <c r="I18" s="128"/>
+      <c r="A18" s="111"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="F18" s="136"/>
+      <c r="G18" s="136"/>
+      <c r="H18" s="136"/>
+      <c r="I18" s="136"/>
       <c r="J18" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="K18" s="134"/>
-      <c r="L18" s="135"/>
-      <c r="M18" s="135"/>
-      <c r="N18" s="136"/>
+      <c r="K18" s="142"/>
+      <c r="L18" s="143"/>
+      <c r="M18" s="143"/>
+      <c r="N18" s="144"/>
     </row>
     <row r="19" spans="1:15" ht="18" customHeight="1">
-      <c r="A19" s="103"/>
-      <c r="B19" s="103"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="103"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="128"/>
-      <c r="I19" s="128"/>
+      <c r="A19" s="111"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="F19" s="136"/>
+      <c r="G19" s="136"/>
+      <c r="H19" s="136"/>
+      <c r="I19" s="136"/>
       <c r="J19" s="31"/>
-      <c r="K19" s="137"/>
-      <c r="L19" s="138"/>
-      <c r="M19" s="138"/>
-      <c r="N19" s="139"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="146"/>
+      <c r="M19" s="146"/>
+      <c r="N19" s="147"/>
     </row>
     <row r="20" spans="1:15" ht="18" customHeight="1">
-      <c r="A20" s="103"/>
-      <c r="B20" s="103"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
-      <c r="F20" s="128"/>
-      <c r="G20" s="128"/>
-      <c r="H20" s="128"/>
-      <c r="I20" s="128"/>
+      <c r="A20" s="111"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
     </row>
     <row r="21" spans="1:15" ht="18" customHeight="1">
-      <c r="A21" s="103"/>
-      <c r="B21" s="103"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="128"/>
-      <c r="H21" s="128"/>
-      <c r="I21" s="128"/>
+      <c r="A21" s="111"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="F21" s="136"/>
+      <c r="G21" s="136"/>
+      <c r="H21" s="136"/>
+      <c r="I21" s="136"/>
       <c r="J21" s="31"/>
-      <c r="K21" s="131" t="s">
+      <c r="K21" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="L21" s="132"/>
-      <c r="M21" s="132"/>
-      <c r="N21" s="133"/>
+      <c r="L21" s="140"/>
+      <c r="M21" s="140"/>
+      <c r="N21" s="141"/>
     </row>
     <row r="22" spans="1:15" ht="18" customHeight="1">
-      <c r="A22" s="103"/>
-      <c r="B22" s="103"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="103"/>
-      <c r="F22" s="128"/>
-      <c r="G22" s="128"/>
-      <c r="H22" s="128"/>
-      <c r="I22" s="128"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="136"/>
       <c r="J22" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="134"/>
-      <c r="L22" s="135"/>
-      <c r="M22" s="135"/>
-      <c r="N22" s="136"/>
+      <c r="K22" s="142"/>
+      <c r="L22" s="143"/>
+      <c r="M22" s="143"/>
+      <c r="N22" s="144"/>
     </row>
     <row r="23" spans="1:15" ht="8.1" customHeight="1">
-      <c r="A23" s="103"/>
-      <c r="B23" s="103"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="128"/>
-      <c r="I23" s="128"/>
+      <c r="A23" s="111"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="111"/>
+      <c r="F23" s="136"/>
+      <c r="G23" s="136"/>
+      <c r="H23" s="136"/>
+      <c r="I23" s="136"/>
       <c r="J23" s="31"/>
-      <c r="K23" s="137"/>
-      <c r="L23" s="138"/>
-      <c r="M23" s="138"/>
-      <c r="N23" s="139"/>
+      <c r="K23" s="145"/>
+      <c r="L23" s="146"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="147"/>
     </row>
     <row r="24" spans="1:15" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="104"/>
-      <c r="C24" s="162"/>
-      <c r="D24" s="162"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="162"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="162"/>
-      <c r="I24" s="162"/>
-      <c r="J24" s="162"/>
-      <c r="K24" s="162"/>
-      <c r="L24" s="162"/>
-      <c r="M24" s="162"/>
-      <c r="N24" s="162"/>
-      <c r="O24" s="162"/>
+      <c r="B24" s="112"/>
+      <c r="C24" s="163"/>
+      <c r="D24" s="163"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="163"/>
+      <c r="G24" s="112"/>
+      <c r="H24" s="163"/>
+      <c r="I24" s="163"/>
+      <c r="J24" s="163"/>
+      <c r="K24" s="163"/>
+      <c r="L24" s="163"/>
+      <c r="M24" s="163"/>
+      <c r="N24" s="163"/>
+      <c r="O24" s="163"/>
     </row>
     <row r="25" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B25" s="98"/>
-      <c r="C25" s="162"/>
-      <c r="D25" s="162"/>
-      <c r="E25" s="100"/>
-      <c r="F25" s="162"/>
-      <c r="G25" s="99"/>
-      <c r="H25" s="162"/>
-      <c r="I25" s="162"/>
-      <c r="J25" s="162"/>
-      <c r="K25" s="162"/>
-      <c r="L25" s="162"/>
-      <c r="M25" s="162"/>
-      <c r="N25" s="162"/>
-      <c r="O25" s="162"/>
+      <c r="B25" s="148"/>
+      <c r="C25" s="163"/>
+      <c r="D25" s="163"/>
+      <c r="E25" s="150"/>
+      <c r="F25" s="163"/>
+      <c r="G25" s="149"/>
+      <c r="H25" s="163"/>
+      <c r="I25" s="163"/>
+      <c r="J25" s="163"/>
+      <c r="K25" s="163"/>
+      <c r="L25" s="163"/>
+      <c r="M25" s="163"/>
+      <c r="N25" s="163"/>
+      <c r="O25" s="163"/>
     </row>
     <row r="26" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B26" s="98"/>
-      <c r="C26" s="162"/>
-      <c r="D26" s="162"/>
-      <c r="E26" s="101" t="s">
+      <c r="B26" s="148"/>
+      <c r="C26" s="163"/>
+      <c r="D26" s="163"/>
+      <c r="E26" s="151" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="102"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="102"/>
+      <c r="F26" s="152"/>
+      <c r="G26" s="152"/>
+      <c r="H26" s="152"/>
       <c r="J26" s="50" t="s">
         <v>19</v>
       </c>
@@ -3676,9 +3666,9 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B27" s="98"/>
-      <c r="C27" s="162"/>
-      <c r="D27" s="162"/>
+      <c r="B27" s="148"/>
+      <c r="C27" s="163"/>
+      <c r="D27" s="163"/>
       <c r="E27" s="38"/>
       <c r="F27" s="39" t="s">
         <v>21</v>
@@ -3692,9 +3682,9 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B28" s="98"/>
-      <c r="C28" s="162"/>
-      <c r="D28" s="162"/>
+      <c r="B28" s="148"/>
+      <c r="C28" s="163"/>
+      <c r="D28" s="163"/>
       <c r="E28" s="40"/>
       <c r="F28" s="39" t="s">
         <v>24</v>
@@ -3708,9 +3698,9 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B29" s="98"/>
-      <c r="C29" s="162"/>
-      <c r="D29" s="162"/>
+      <c r="B29" s="148"/>
+      <c r="C29" s="163"/>
+      <c r="D29" s="163"/>
       <c r="E29" s="41"/>
       <c r="F29" s="39" t="s">
         <v>26</v>
@@ -3745,13 +3735,14 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A1:AI1"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G25:O25"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:H26"/>
     <mergeCell ref="A5:D23"/>
     <mergeCell ref="G24:O24"/>
     <mergeCell ref="B24:D24"/>
@@ -3765,14 +3756,13 @@
     <mergeCell ref="K13:N15"/>
     <mergeCell ref="K17:N19"/>
     <mergeCell ref="K21:N23"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G25:O25"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="F3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3893,7 +3883,7 @@
       <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="90" t="s">
+      <c r="D9" s="162" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3916,7 +3906,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="164" t="s">
         <v>47</v>
       </c>
       <c r="B1" s="153"/>
@@ -4297,7 +4287,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="164" t="s">
         <v>47</v>
       </c>
       <c r="B1" s="153"/>
@@ -4353,7 +4343,7 @@
       <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="163" t="s">
+      <c r="A5" s="164" t="s">
         <v>107</v>
       </c>
       <c r="B5" s="153"/>
@@ -5325,12 +5315,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5506,17 +5497,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F5D78C1-8A47-4B3E-B0AF-72715DE99B9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63EC841B-EE2F-404B-AE20-759328EC6A01}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5524,5 +5514,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63EC841B-EE2F-404B-AE20-759328EC6A01}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F5D78C1-8A47-4B3E-B0AF-72715DE99B9C}"/>
 </file>